--- a/Data/WBID_criteria.xlsx
+++ b/Data/WBID_criteria.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://pinellasgov.sharepoint.com/sites/BCC-PW-ENVMT/Monitoring and Assessment/R/water_quality_dashboard/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="331" documentId="13_ncr:1_{7A309D96-916D-4D0A-99DA-2AF397C66AE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{28538134-16A2-4545-ADB8-D30C4AFCB236}"/>
+  <xr:revisionPtr revIDLastSave="367" documentId="13_ncr:1_{7A309D96-916D-4D0A-99DA-2AF397C66AE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{59498A41-9B89-41DE-8B71-53A1CBDD27E0}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{BE13FCFD-69C3-482F-A9D3-58396836E9E2}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{BE13FCFD-69C3-482F-A9D3-58396836E9E2}"/>
   </bookViews>
   <sheets>
     <sheet name="Criteria" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="681" uniqueCount="290">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="709" uniqueCount="307">
   <si>
     <t>WBID</t>
   </si>
@@ -911,6 +911,57 @@
   </si>
   <si>
     <t>MARINE</t>
+  </si>
+  <si>
+    <t>23-04</t>
+  </si>
+  <si>
+    <t>1694C</t>
+  </si>
+  <si>
+    <t>DIRECT RUNOFF TO BAY</t>
+  </si>
+  <si>
+    <t>1731B</t>
+  </si>
+  <si>
+    <t>SALT CREEK</t>
+  </si>
+  <si>
+    <t>1731A</t>
+  </si>
+  <si>
+    <t>LAKE MAGGIORE</t>
+  </si>
+  <si>
+    <t>1700A</t>
+  </si>
+  <si>
+    <t>CRESCENT LAKE</t>
+  </si>
+  <si>
+    <t>1716B</t>
+  </si>
+  <si>
+    <t>CLAB BAYOU DRAIN</t>
+  </si>
+  <si>
+    <t>1716C1</t>
+  </si>
+  <si>
+    <t>CLAM BAYOU (EAST DRAINAGE-NORTH)</t>
+  </si>
+  <si>
+    <t>1716C2</t>
+  </si>
+  <si>
+    <t>CLAM BAYOU (EAST DRAINAGE-SOUTH)</t>
+  </si>
+  <si>
+    <t>1709B</t>
+  </si>
+  <si>
+    <t>DIRECT RUNOFF TO BAY (YACHT BASIN - BASIN A)</t>
   </si>
 </sst>
 </file>
@@ -956,20 +1007,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -986,6 +1031,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1285,22 +1334,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0CEB8270-E891-48E2-9417-9A696D4AB26E}">
-  <dimension ref="A1:I74"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:I82"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="7.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="46.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="46.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="7" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="7.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="9" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="16384" width="9.109375" style="1"/>
+    <col min="9" max="9" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1325,11 +1374,11 @@
       <c r="H1" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="1" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>1474</v>
       </c>
@@ -1355,7 +1404,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>1475</v>
       </c>
@@ -1381,7 +1430,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>1529</v>
       </c>
@@ -1407,7 +1456,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>1550</v>
       </c>
@@ -1433,7 +1482,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>11</v>
       </c>
@@ -1459,7 +1508,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>13</v>
       </c>
@@ -1485,7 +1534,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>17</v>
       </c>
@@ -1511,7 +1560,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>22</v>
       </c>
@@ -1537,7 +1586,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>1696</v>
       </c>
@@ -1563,7 +1612,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>2</v>
       </c>
@@ -1589,7 +1638,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>5</v>
       </c>
@@ -1615,7 +1664,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>3</v>
       </c>
@@ -1641,7 +1690,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>7</v>
       </c>
@@ -1667,7 +1716,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>4</v>
       </c>
@@ -1693,7 +1742,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>8</v>
       </c>
@@ -1719,7 +1768,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>27</v>
       </c>
@@ -1745,7 +1794,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>12</v>
       </c>
@@ -1771,7 +1820,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1797,7 +1846,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>9</v>
       </c>
@@ -1823,7 +1872,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>10</v>
       </c>
@@ -1849,11 +1898,11 @@
         <v>410</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A22" s="2" t="s">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B22" s="2" t="s">
+      <c r="B22" s="1" t="s">
         <v>121</v>
       </c>
       <c r="C22" s="1" t="s">
@@ -1875,7 +1924,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>29</v>
       </c>
@@ -1901,7 +1950,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>217</v>
       </c>
@@ -1927,7 +1976,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>21</v>
       </c>
@@ -1953,7 +2002,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
         <v>18</v>
       </c>
@@ -1979,7 +2028,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
         <v>141</v>
       </c>
@@ -2005,7 +2054,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
         <v>142</v>
       </c>
@@ -2031,7 +2080,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
         <v>30</v>
       </c>
@@ -2057,7 +2106,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
         <v>23</v>
       </c>
@@ -2083,7 +2132,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2109,7 +2158,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
         <v>24</v>
       </c>
@@ -2135,7 +2184,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
         <v>25</v>
       </c>
@@ -2161,7 +2210,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
         <v>272</v>
       </c>
@@ -2187,7 +2236,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
         <v>31</v>
       </c>
@@ -2213,7 +2262,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
         <v>37</v>
       </c>
@@ -2239,7 +2288,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
         <v>38</v>
       </c>
@@ -2265,7 +2314,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
         <v>36</v>
       </c>
@@ -2291,7 +2340,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
         <v>41</v>
       </c>
@@ -2317,7 +2366,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
         <v>42</v>
       </c>
@@ -2343,7 +2392,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" s="1">
         <v>1528</v>
       </c>
@@ -2366,7 +2415,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" s="1">
         <v>1661</v>
       </c>
@@ -2389,7 +2438,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" s="1">
         <v>8045</v>
       </c>
@@ -2412,7 +2461,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
         <v>48</v>
       </c>
@@ -2435,7 +2484,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
         <v>47</v>
       </c>
@@ -2458,7 +2507,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
         <v>52</v>
       </c>
@@ -2481,7 +2530,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
         <v>53</v>
       </c>
@@ -2504,7 +2553,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
         <v>46</v>
       </c>
@@ -2527,7 +2576,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
         <v>45</v>
       </c>
@@ -2550,7 +2599,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
         <v>44</v>
       </c>
@@ -2573,7 +2622,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
         <v>73</v>
       </c>
@@ -2596,7 +2645,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
         <v>54</v>
       </c>
@@ -2619,7 +2668,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
         <v>51</v>
       </c>
@@ -2642,7 +2691,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
         <v>49</v>
       </c>
@@ -2665,7 +2714,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
         <v>55</v>
       </c>
@@ -2688,7 +2737,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
         <v>50</v>
       </c>
@@ -2711,7 +2760,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A57" s="1">
         <v>1440</v>
       </c>
@@ -2722,13 +2771,13 @@
         <v>35</v>
       </c>
       <c r="D57" s="1">
-        <v>11</v>
+        <v>3.8</v>
       </c>
       <c r="E57" s="1">
-        <v>1.54</v>
+        <v>0.65</v>
       </c>
       <c r="F57" s="1">
-        <v>0.12</v>
+        <v>6.3E-2</v>
       </c>
       <c r="G57" s="1">
         <v>38</v>
@@ -2737,7 +2786,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
         <v>1</v>
       </c>
@@ -2763,7 +2812,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A59" s="1">
         <v>1530</v>
       </c>
@@ -2789,7 +2838,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
         <v>6</v>
       </c>
@@ -2815,7 +2864,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A61" s="1">
         <v>1569</v>
       </c>
@@ -2841,7 +2890,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
         <v>15</v>
       </c>
@@ -2867,7 +2916,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
         <v>20</v>
       </c>
@@ -2893,7 +2942,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A64" s="1">
         <v>1633</v>
       </c>
@@ -2919,7 +2968,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
         <v>19</v>
       </c>
@@ -2945,7 +2994,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A66" s="1">
         <v>1683</v>
       </c>
@@ -2971,7 +3020,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A67" s="1">
         <v>1700</v>
       </c>
@@ -2997,7 +3046,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
         <v>158</v>
       </c>
@@ -3023,7 +3072,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
         <v>287</v>
       </c>
@@ -3049,7 +3098,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
         <v>16</v>
       </c>
@@ -3075,14 +3124,14 @@
         <v>130</v>
       </c>
     </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
         <v>269</v>
       </c>
-      <c r="B71" s="5" t="s">
+      <c r="B71" s="1" t="s">
         <v>268</v>
       </c>
-      <c r="C71" s="5" t="s">
+      <c r="C71" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D71" s="1">
@@ -3101,7 +3150,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
         <v>33</v>
       </c>
@@ -3127,7 +3176,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
         <v>34</v>
       </c>
@@ -3153,7 +3202,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="74" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
         <v>279</v>
       </c>
@@ -3176,6 +3225,214 @@
         <v>38</v>
       </c>
       <c r="I74" s="1">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="75" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A75" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="B75" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="C75" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D75" s="1">
+        <v>11</v>
+      </c>
+      <c r="E75" s="1">
+        <v>1.54</v>
+      </c>
+      <c r="F75" s="1">
+        <v>0.12</v>
+      </c>
+      <c r="G75" s="1">
+        <v>38</v>
+      </c>
+      <c r="I75" s="1">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="76" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A76" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="B76" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="C76" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="D76" s="1">
+        <v>11</v>
+      </c>
+      <c r="E76" s="1">
+        <v>1.54</v>
+      </c>
+      <c r="F76" s="1">
+        <v>0.12</v>
+      </c>
+      <c r="G76" s="1">
+        <v>38</v>
+      </c>
+      <c r="I76" s="1">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="77" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A77" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="B77" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="C77" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="D77" s="1">
+        <v>20</v>
+      </c>
+      <c r="E77" s="1">
+        <v>1.91</v>
+      </c>
+      <c r="F77" s="1">
+        <v>0.09</v>
+      </c>
+      <c r="G77" s="1">
+        <v>38</v>
+      </c>
+      <c r="H77" s="1">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="78" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A78" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="B78" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="C78" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="D78" s="1">
+        <v>20</v>
+      </c>
+      <c r="E78" s="1">
+        <v>1.91</v>
+      </c>
+      <c r="F78" s="1">
+        <v>0.09</v>
+      </c>
+      <c r="G78" s="1">
+        <v>38</v>
+      </c>
+      <c r="H78" s="1">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="79" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A79" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="B79" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="C79" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D79" s="1">
+        <v>20</v>
+      </c>
+      <c r="E79" s="1">
+        <v>1.54</v>
+      </c>
+      <c r="F79" s="1">
+        <v>0.12</v>
+      </c>
+      <c r="G79" s="1">
+        <v>38</v>
+      </c>
+      <c r="H79" s="1">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="80" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A80" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="B80" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="C80" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D80" s="1">
+        <v>11</v>
+      </c>
+      <c r="E80" s="1">
+        <v>1.54</v>
+      </c>
+      <c r="F80" s="1">
+        <v>0.12</v>
+      </c>
+      <c r="G80" s="1">
+        <v>38</v>
+      </c>
+      <c r="I80" s="1">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="81" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A81" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="B81" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="C81" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="D81" s="1">
+        <v>11</v>
+      </c>
+      <c r="E81" s="1">
+        <v>1.54</v>
+      </c>
+      <c r="F81" s="1">
+        <v>0.12</v>
+      </c>
+      <c r="G81" s="1">
+        <v>38</v>
+      </c>
+      <c r="I81" s="1">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="82" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A82" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="B82" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="C82" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="D82" s="1">
+        <v>11</v>
+      </c>
+      <c r="E82" s="1">
+        <v>1.54</v>
+      </c>
+      <c r="F82" s="1">
+        <v>0.12</v>
+      </c>
+      <c r="G82" s="1">
+        <v>38</v>
+      </c>
+      <c r="I82" s="1">
         <v>130</v>
       </c>
     </row>
@@ -3190,13 +3447,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B694CC09-0A0D-4CFC-A36A-4C4F0190FC8F}">
   <dimension ref="A1:B7"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>56</v>
       </c>
@@ -3204,7 +3461,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>58</v>
       </c>
@@ -3212,7 +3469,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>61</v>
       </c>
@@ -3220,7 +3477,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>62</v>
       </c>
@@ -3228,7 +3485,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>63</v>
       </c>
@@ -3236,7 +3493,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>64</v>
       </c>
@@ -3244,7 +3501,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>43</v>
       </c>
@@ -3259,18 +3516,18 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{446DEF65-5E77-4BAF-B17C-A7715D6429D1}">
-  <dimension ref="A1:F113"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:F114"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="46.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.6640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="7.109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.5546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="5.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="46.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>144</v>
       </c>
@@ -3290,7 +3547,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>147</v>
       </c>
@@ -3303,14 +3560,14 @@
       <c r="D2" t="s">
         <v>148</v>
       </c>
-      <c r="E2" s="3">
+      <c r="E2" s="2">
         <v>28.157197</v>
       </c>
-      <c r="F2" s="3">
+      <c r="F2" s="2">
         <v>-82.757036999999997</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>149</v>
       </c>
@@ -3323,14 +3580,14 @@
       <c r="D3" t="s">
         <v>148</v>
       </c>
-      <c r="E3" s="3">
+      <c r="E3" s="2">
         <v>28.173974999999999</v>
       </c>
-      <c r="F3" s="3">
+      <c r="F3" s="2">
         <v>-82.722536000000005</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>150</v>
       </c>
@@ -3343,14 +3600,14 @@
       <c r="D4" t="s">
         <v>148</v>
       </c>
-      <c r="E4" s="3">
+      <c r="E4" s="2">
         <v>28.174032</v>
       </c>
-      <c r="F4" s="3">
+      <c r="F4" s="2">
         <v>-82.723491999999993</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>151</v>
       </c>
@@ -3363,14 +3620,14 @@
       <c r="D5" t="s">
         <v>152</v>
       </c>
-      <c r="E5" s="3">
+      <c r="E5" s="2">
         <v>28.162289999999999</v>
       </c>
-      <c r="F5" s="3">
+      <c r="F5" s="2">
         <v>-82.710830000000001</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>153</v>
       </c>
@@ -3383,14 +3640,14 @@
       <c r="D6" t="s">
         <v>152</v>
       </c>
-      <c r="E6" s="3">
+      <c r="E6" s="2">
         <v>28.151558000000001</v>
       </c>
-      <c r="F6" s="3">
+      <c r="F6" s="2">
         <v>-82.696158999999994</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>154</v>
       </c>
@@ -3403,14 +3660,14 @@
       <c r="D7" t="s">
         <v>152</v>
       </c>
-      <c r="E7" s="3">
+      <c r="E7" s="2">
         <v>28.165811999999999</v>
       </c>
-      <c r="F7" s="3">
+      <c r="F7" s="2">
         <v>-82.697146000000004</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>155</v>
       </c>
@@ -3423,14 +3680,14 @@
       <c r="D8" t="s">
         <v>148</v>
       </c>
-      <c r="E8" s="3">
+      <c r="E8" s="2">
         <v>28.163824999999999</v>
       </c>
-      <c r="F8" s="3">
+      <c r="F8" s="2">
         <v>-82.740590999999995</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>156</v>
       </c>
@@ -3443,14 +3700,14 @@
       <c r="D9" t="s">
         <v>158</v>
       </c>
-      <c r="E9" s="3">
+      <c r="E9" s="2">
         <v>28.147479000000001</v>
       </c>
-      <c r="F9" s="3">
+      <c r="F9" s="2">
         <v>-82.764122999999998</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>159</v>
       </c>
@@ -3463,14 +3720,14 @@
       <c r="D10" t="s">
         <v>158</v>
       </c>
-      <c r="E10" s="3">
+      <c r="E10" s="2">
         <v>28.153013000000001</v>
       </c>
-      <c r="F10" s="3">
+      <c r="F10" s="2">
         <v>-82.765980999999996</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>160</v>
       </c>
@@ -3483,14 +3740,14 @@
       <c r="D11" t="s">
         <v>158</v>
       </c>
-      <c r="E11" s="4">
+      <c r="E11" s="3">
         <v>28.148797999999999</v>
       </c>
-      <c r="F11" s="4">
+      <c r="F11" s="3">
         <v>-82.770308999999997</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>161</v>
       </c>
@@ -3503,14 +3760,14 @@
       <c r="D12" t="s">
         <v>1</v>
       </c>
-      <c r="E12" s="3">
+      <c r="E12" s="2">
         <v>28.116945000000001</v>
       </c>
-      <c r="F12" s="3">
+      <c r="F12" s="2">
         <v>-82.765307000000007</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>163</v>
       </c>
@@ -3523,14 +3780,14 @@
       <c r="D13" t="s">
         <v>1</v>
       </c>
-      <c r="E13" s="3">
+      <c r="E13" s="2">
         <v>28.115624</v>
       </c>
-      <c r="F13" s="3">
+      <c r="F13" s="2">
         <v>-82.764602999999994</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>164</v>
       </c>
@@ -3543,14 +3800,14 @@
       <c r="D14" t="s">
         <v>2</v>
       </c>
-      <c r="E14" s="3">
+      <c r="E14" s="2">
         <v>28.111719000000001</v>
       </c>
-      <c r="F14" s="3">
+      <c r="F14" s="2">
         <v>-82.761505999999997</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>165</v>
       </c>
@@ -3563,14 +3820,14 @@
       <c r="D15" t="s">
         <v>166</v>
       </c>
-      <c r="E15" s="3">
+      <c r="E15" s="2">
         <v>28.140872000000002</v>
       </c>
-      <c r="F15" s="3">
+      <c r="F15" s="2">
         <v>-82.639453000000003</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>167</v>
       </c>
@@ -3583,14 +3840,14 @@
       <c r="D16" t="s">
         <v>166</v>
       </c>
-      <c r="E16" s="3">
+      <c r="E16" s="2">
         <v>28.086324999999999</v>
       </c>
-      <c r="F16" s="3">
+      <c r="F16" s="2">
         <v>-82.694147999999998</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>168</v>
       </c>
@@ -3603,14 +3860,14 @@
       <c r="D17" t="s">
         <v>166</v>
       </c>
-      <c r="E17" s="3">
+      <c r="E17" s="2">
         <v>28.076658999999999</v>
       </c>
-      <c r="F17" s="3">
+      <c r="F17" s="2">
         <v>-82.697884999999999</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>169</v>
       </c>
@@ -3623,14 +3880,14 @@
       <c r="D18" t="s">
         <v>170</v>
       </c>
-      <c r="E18" s="3">
+      <c r="E18" s="2">
         <v>28.046462999999999</v>
       </c>
-      <c r="F18" s="3">
+      <c r="F18" s="2">
         <v>-82.691727</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>171</v>
       </c>
@@ -3643,14 +3900,14 @@
       <c r="D19" t="s">
         <v>3</v>
       </c>
-      <c r="E19" s="3">
+      <c r="E19" s="2">
         <v>28.0456</v>
       </c>
-      <c r="F19" s="3">
+      <c r="F19" s="2">
         <v>-82.684650000000005</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>172</v>
       </c>
@@ -3663,14 +3920,14 @@
       <c r="D20" t="s">
         <v>3</v>
       </c>
-      <c r="E20" s="3">
+      <c r="E20" s="2">
         <v>28.050713999999999</v>
       </c>
-      <c r="F20" s="3">
+      <c r="F20" s="2">
         <v>-82.694044000000005</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>173</v>
       </c>
@@ -3683,14 +3940,14 @@
       <c r="D21" t="s">
         <v>174</v>
       </c>
-      <c r="E21" s="3">
+      <c r="E21" s="2">
         <v>28.068168</v>
       </c>
-      <c r="F21" s="3">
+      <c r="F21" s="2">
         <v>-82.722860999999995</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>175</v>
       </c>
@@ -3703,14 +3960,14 @@
       <c r="D22" t="s">
         <v>4</v>
       </c>
-      <c r="E22" s="3">
+      <c r="E22" s="2">
         <v>28.052875</v>
       </c>
-      <c r="F22" s="3">
+      <c r="F22" s="2">
         <v>-82.709120999999996</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>176</v>
       </c>
@@ -3723,14 +3980,14 @@
       <c r="D23" t="s">
         <v>4</v>
       </c>
-      <c r="E23" s="3">
+      <c r="E23" s="2">
         <v>28.061199999999999</v>
       </c>
-      <c r="F23" s="3">
+      <c r="F23" s="2">
         <v>-82.710400000000007</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>177</v>
       </c>
@@ -3743,14 +4000,14 @@
       <c r="D24" t="s">
         <v>5</v>
       </c>
-      <c r="E24" s="3">
+      <c r="E24" s="2">
         <v>28.068487999999999</v>
       </c>
-      <c r="F24" s="3">
+      <c r="F24" s="2">
         <v>-82.768835999999993</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>178</v>
       </c>
@@ -3763,14 +4020,14 @@
       <c r="D25" t="s">
         <v>6</v>
       </c>
-      <c r="E25" s="3">
+      <c r="E25" s="2">
         <v>28.033753999999998</v>
       </c>
-      <c r="F25" s="3">
+      <c r="F25" s="2">
         <v>-82.780066000000005</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>179</v>
       </c>
@@ -3783,14 +4040,14 @@
       <c r="D26" t="s">
         <v>27</v>
       </c>
-      <c r="E26" s="3">
+      <c r="E26" s="2">
         <v>28.033784000000001</v>
       </c>
-      <c r="F26" s="3">
+      <c r="F26" s="2">
         <v>-82.776065000000003</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>180</v>
       </c>
@@ -3803,14 +4060,14 @@
       <c r="D27" t="s">
         <v>7</v>
       </c>
-      <c r="E27" s="3">
+      <c r="E27" s="2">
         <v>28.046779000000001</v>
       </c>
-      <c r="F27" s="3">
+      <c r="F27" s="2">
         <v>-82.759876000000006</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>181</v>
       </c>
@@ -3823,14 +4080,14 @@
       <c r="D28" t="s">
         <v>182</v>
       </c>
-      <c r="E28" s="3">
+      <c r="E28" s="2">
         <v>28.04138</v>
       </c>
-      <c r="F28" s="3">
+      <c r="F28" s="2">
         <v>-82.753029999999995</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>183</v>
       </c>
@@ -3843,14 +4100,14 @@
       <c r="D29">
         <v>1550</v>
       </c>
-      <c r="E29" s="3">
+      <c r="E29" s="2">
         <v>28.005400000000002</v>
       </c>
-      <c r="F29" s="3">
+      <c r="F29" s="2">
         <v>-82.7547</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>184</v>
       </c>
@@ -3863,14 +4120,14 @@
       <c r="D30" t="s">
         <v>7</v>
       </c>
-      <c r="E30" s="3">
+      <c r="E30" s="2">
         <v>28.03445</v>
       </c>
-      <c r="F30" s="3">
+      <c r="F30" s="2">
         <v>-82.737899999999996</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>185</v>
       </c>
@@ -3883,14 +4140,14 @@
       <c r="D31" t="s">
         <v>7</v>
       </c>
-      <c r="E31" s="3">
+      <c r="E31" s="2">
         <v>28.023250000000001</v>
       </c>
-      <c r="F31" s="3">
+      <c r="F31" s="2">
         <v>-82.740549999999999</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>186</v>
       </c>
@@ -3903,14 +4160,14 @@
       <c r="D32" t="s">
         <v>7</v>
       </c>
-      <c r="E32" s="3">
+      <c r="E32" s="2">
         <v>28.040410000000001</v>
       </c>
-      <c r="F32" s="3">
+      <c r="F32" s="2">
         <v>-82.746799999999993</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>187</v>
       </c>
@@ -3923,14 +4180,14 @@
       <c r="D33" t="s">
         <v>7</v>
       </c>
-      <c r="E33" s="3">
+      <c r="E33" s="2">
         <v>28.032423000000001</v>
       </c>
-      <c r="F33" s="3">
+      <c r="F33" s="2">
         <v>-82.737782999999993</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>188</v>
       </c>
@@ -3943,14 +4200,14 @@
       <c r="D34" t="s">
         <v>8</v>
       </c>
-      <c r="E34" s="3">
+      <c r="E34" s="2">
         <v>28.037299999999998</v>
       </c>
-      <c r="F34" s="3">
+      <c r="F34" s="2">
         <v>-82.703731000000005</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>189</v>
       </c>
@@ -3963,14 +4220,14 @@
       <c r="D35" t="s">
         <v>191</v>
       </c>
-      <c r="E35" s="3">
+      <c r="E35" s="2">
         <v>28.020367</v>
       </c>
-      <c r="F35" s="3">
+      <c r="F35" s="2">
         <v>-82.689852999999999</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>192</v>
       </c>
@@ -3983,14 +4240,14 @@
       <c r="D36" t="s">
         <v>9</v>
       </c>
-      <c r="E36" s="3">
+      <c r="E36" s="2">
         <v>28.012889000000001</v>
       </c>
-      <c r="F36" s="3">
+      <c r="F36" s="2">
         <v>-82.701791</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>193</v>
       </c>
@@ -4003,14 +4260,14 @@
       <c r="D37" t="s">
         <v>9</v>
       </c>
-      <c r="E37" s="3">
+      <c r="E37" s="2">
         <v>28.014890999999999</v>
       </c>
-      <c r="F37" s="3">
+      <c r="F37" s="2">
         <v>-82.698875999999998</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>194</v>
       </c>
@@ -4023,14 +4280,14 @@
       <c r="D38" t="s">
         <v>9</v>
       </c>
-      <c r="E38" s="3">
+      <c r="E38" s="2">
         <v>28.014676000000001</v>
       </c>
-      <c r="F38" s="3">
+      <c r="F38" s="2">
         <v>-82.696267000000006</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>195</v>
       </c>
@@ -4043,14 +4300,14 @@
       <c r="D39" t="s">
         <v>10</v>
       </c>
-      <c r="E39" s="3">
+      <c r="E39" s="2">
         <v>27.996171</v>
       </c>
-      <c r="F39" s="3">
+      <c r="F39" s="2">
         <v>-82.692380999999997</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>196</v>
       </c>
@@ -4063,14 +4320,14 @@
       <c r="D40" t="s">
         <v>10</v>
       </c>
-      <c r="E40" s="3">
+      <c r="E40" s="2">
         <v>27.996813</v>
       </c>
-      <c r="F40" s="3">
+      <c r="F40" s="2">
         <v>-82.694027000000006</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>197</v>
       </c>
@@ -4083,14 +4340,14 @@
       <c r="D41" t="s">
         <v>36</v>
       </c>
-      <c r="E41" s="3">
+      <c r="E41" s="2">
         <v>28.002573000000002</v>
       </c>
-      <c r="F41" s="3">
+      <c r="F41" s="2">
         <v>-82.721708000000007</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>198</v>
       </c>
@@ -4103,14 +4360,14 @@
       <c r="D42" t="s">
         <v>38</v>
       </c>
-      <c r="E42" s="3">
+      <c r="E42" s="2">
         <v>27.979585</v>
       </c>
-      <c r="F42" s="3">
+      <c r="F42" s="2">
         <v>-82.695250000000001</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>199</v>
       </c>
@@ -4123,14 +4380,14 @@
       <c r="D43" t="s">
         <v>28</v>
       </c>
-      <c r="E43" s="3">
+      <c r="E43" s="2">
         <v>27.989871999999998</v>
       </c>
-      <c r="F43" s="3">
+      <c r="F43" s="2">
         <v>-82.747136999999995</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>200</v>
       </c>
@@ -4143,14 +4400,14 @@
       <c r="D44" t="s">
         <v>11</v>
       </c>
-      <c r="E44" s="3">
+      <c r="E44" s="2">
         <v>27.974701</v>
       </c>
-      <c r="F44" s="3">
+      <c r="F44" s="2">
         <v>-82.713548000000003</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>201</v>
       </c>
@@ -4163,14 +4420,14 @@
       <c r="D45" t="s">
         <v>11</v>
       </c>
-      <c r="E45" s="3">
+      <c r="E45" s="2">
         <v>27.974450999999998</v>
       </c>
-      <c r="F45" s="3">
+      <c r="F45" s="2">
         <v>-82.725444999999993</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>202</v>
       </c>
@@ -4183,14 +4440,14 @@
       <c r="D46" t="s">
         <v>28</v>
       </c>
-      <c r="E46" s="3">
+      <c r="E46" s="2">
         <v>27.992194000000001</v>
       </c>
-      <c r="F46" s="3">
+      <c r="F46" s="2">
         <v>-82.748092999999997</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>203</v>
       </c>
@@ -4203,14 +4460,14 @@
       <c r="D47" t="s">
         <v>12</v>
       </c>
-      <c r="E47" s="3">
+      <c r="E47" s="2">
         <v>27.990174</v>
       </c>
-      <c r="F47" s="3">
+      <c r="F47" s="2">
         <v>-82.783998999999994</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>204</v>
       </c>
@@ -4223,14 +4480,14 @@
       <c r="D48" t="s">
         <v>13</v>
       </c>
-      <c r="E48" s="3">
+      <c r="E48" s="2">
         <v>27.943531</v>
       </c>
-      <c r="F48" s="3">
+      <c r="F48" s="2">
         <v>-82.805969000000005</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>205</v>
       </c>
@@ -4243,14 +4500,14 @@
       <c r="D49" t="s">
         <v>13</v>
       </c>
-      <c r="E49" s="3">
+      <c r="E49" s="2">
         <v>27.940683</v>
       </c>
-      <c r="F49" s="3">
+      <c r="F49" s="2">
         <v>-82.801349000000002</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>206</v>
       </c>
@@ -4263,14 +4520,14 @@
       <c r="D50" t="s">
         <v>14</v>
       </c>
-      <c r="E50" s="3">
+      <c r="E50" s="2">
         <v>27.967907</v>
       </c>
-      <c r="F50" s="3">
+      <c r="F50" s="2">
         <v>-82.781784999999999</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>207</v>
       </c>
@@ -4283,14 +4540,14 @@
       <c r="D51" t="s">
         <v>14</v>
       </c>
-      <c r="E51" s="3">
+      <c r="E51" s="2">
         <v>27.971475000000002</v>
       </c>
-      <c r="F51" s="3">
+      <c r="F51" s="2">
         <v>-82.781530000000004</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>208</v>
       </c>
@@ -4303,14 +4560,14 @@
       <c r="D52" t="s">
         <v>15</v>
       </c>
-      <c r="E52" s="3">
+      <c r="E52" s="2">
         <v>27.928132999999999</v>
       </c>
-      <c r="F52" s="3">
+      <c r="F52" s="2">
         <v>-82.745982999999995</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>209</v>
       </c>
@@ -4323,14 +4580,14 @@
       <c r="D53" t="s">
         <v>15</v>
       </c>
-      <c r="E53" s="3">
+      <c r="E53" s="2">
         <v>27.935396999999998</v>
       </c>
-      <c r="F53" s="3">
+      <c r="F53" s="2">
         <v>-82.751176000000001</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>210</v>
       </c>
@@ -4343,14 +4600,14 @@
       <c r="D54" t="s">
         <v>15</v>
       </c>
-      <c r="E54" s="3">
+      <c r="E54" s="2">
         <v>27.938490000000002</v>
       </c>
-      <c r="F54" s="3">
+      <c r="F54" s="2">
         <v>-82.758813000000004</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>211</v>
       </c>
@@ -4363,14 +4620,14 @@
       <c r="D55" t="s">
         <v>29</v>
       </c>
-      <c r="E55" s="3">
+      <c r="E55" s="2">
         <v>27.950747</v>
       </c>
-      <c r="F55" s="3">
+      <c r="F55" s="2">
         <v>-82.754149999999996</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>212</v>
       </c>
@@ -4383,14 +4640,14 @@
       <c r="D56" t="s">
         <v>29</v>
       </c>
-      <c r="E56" s="3">
+      <c r="E56" s="2">
         <v>27.9407</v>
       </c>
-      <c r="F56" s="3">
+      <c r="F56" s="2">
         <v>-82.759795999999994</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>213</v>
       </c>
@@ -4403,14 +4660,14 @@
       <c r="D57" t="s">
         <v>29</v>
       </c>
-      <c r="E57" s="3">
+      <c r="E57" s="2">
         <v>27.938783000000001</v>
       </c>
-      <c r="F57" s="3">
+      <c r="F57" s="2">
         <v>-82.750726999999998</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>215</v>
       </c>
@@ -4423,14 +4680,14 @@
       <c r="D58" t="s">
         <v>217</v>
       </c>
-      <c r="E58" s="3">
+      <c r="E58" s="2">
         <v>27.927420000000001</v>
       </c>
-      <c r="F58" s="3">
+      <c r="F58" s="2">
         <v>-82.738349999999997</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>214</v>
       </c>
@@ -4443,14 +4700,14 @@
       <c r="D59" t="s">
         <v>29</v>
       </c>
-      <c r="E59" s="3">
+      <c r="E59" s="2">
         <v>27.927600000000002</v>
       </c>
-      <c r="F59" s="3">
+      <c r="F59" s="2">
         <v>-82.762150000000005</v>
       </c>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>218</v>
       </c>
@@ -4463,14 +4720,14 @@
       <c r="D60" t="s">
         <v>29</v>
       </c>
-      <c r="E60" s="3">
+      <c r="E60" s="2">
         <v>27.94068</v>
       </c>
-      <c r="F60" s="3">
+      <c r="F60" s="2">
         <v>-82.750590000000003</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>219</v>
       </c>
@@ -4483,14 +4740,14 @@
       <c r="D61" t="s">
         <v>29</v>
       </c>
-      <c r="E61" s="3">
+      <c r="E61" s="2">
         <v>27.940999999999999</v>
       </c>
-      <c r="F61" s="3">
+      <c r="F61" s="2">
         <v>-82.742400000000004</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>220</v>
       </c>
@@ -4503,14 +4760,14 @@
       <c r="D62" t="s">
         <v>29</v>
       </c>
-      <c r="E62" s="3">
+      <c r="E62" s="2">
         <v>27.960999999999999</v>
       </c>
-      <c r="F62" s="3">
+      <c r="F62" s="2">
         <v>-82.759609999999995</v>
       </c>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>221</v>
       </c>
@@ -4523,14 +4780,14 @@
       <c r="D63" t="s">
         <v>29</v>
       </c>
-      <c r="E63" s="3">
+      <c r="E63" s="2">
         <v>27.93121</v>
       </c>
-      <c r="F63" s="3">
+      <c r="F63" s="2">
         <v>-82.757800000000003</v>
       </c>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>222</v>
       </c>
@@ -4543,14 +4800,14 @@
       <c r="D64" t="s">
         <v>16</v>
       </c>
-      <c r="E64" s="3">
+      <c r="E64" s="2">
         <v>27.923224999999999</v>
       </c>
-      <c r="F64" s="3">
+      <c r="F64" s="2">
         <v>-82.717813000000007</v>
       </c>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>223</v>
       </c>
@@ -4563,14 +4820,14 @@
       <c r="D65" t="s">
         <v>17</v>
       </c>
-      <c r="E65" s="3">
+      <c r="E65" s="2">
         <v>27.917581999999999</v>
       </c>
-      <c r="F65" s="3">
+      <c r="F65" s="2">
         <v>-82.722548000000003</v>
       </c>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>224</v>
       </c>
@@ -4583,14 +4840,14 @@
       <c r="D66" t="s">
         <v>17</v>
       </c>
-      <c r="E66" s="3">
+      <c r="E66" s="2">
         <v>27.911640999999999</v>
       </c>
-      <c r="F66" s="3">
+      <c r="F66" s="2">
         <v>-82.725682000000006</v>
       </c>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>225</v>
       </c>
@@ -4603,14 +4860,14 @@
       <c r="D67" t="s">
         <v>17</v>
       </c>
-      <c r="E67" s="3">
+      <c r="E67" s="2">
         <v>27.911525999999999</v>
       </c>
-      <c r="F67" s="3">
+      <c r="F67" s="2">
         <v>-82.725611000000001</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>226</v>
       </c>
@@ -4623,14 +4880,14 @@
       <c r="D68" t="s">
         <v>17</v>
       </c>
-      <c r="E68" s="3">
+      <c r="E68" s="2">
         <v>27.915656999999999</v>
       </c>
-      <c r="F68" s="3">
+      <c r="F68" s="2">
         <v>-82.725143000000003</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>227</v>
       </c>
@@ -4643,14 +4900,14 @@
       <c r="D69" t="s">
         <v>17</v>
       </c>
-      <c r="E69" s="3">
+      <c r="E69" s="2">
         <v>27.914597000000001</v>
       </c>
-      <c r="F69" s="3">
+      <c r="F69" s="2">
         <v>-82.730187999999998</v>
       </c>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>228</v>
       </c>
@@ -4663,14 +4920,14 @@
       <c r="D70" t="s">
         <v>17</v>
       </c>
-      <c r="E70" s="3">
+      <c r="E70" s="2">
         <v>27.913191000000001</v>
       </c>
-      <c r="F70" s="3">
+      <c r="F70" s="2">
         <v>-82.732553999999993</v>
       </c>
     </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>229</v>
       </c>
@@ -4683,14 +4940,14 @@
       <c r="D71" t="s">
         <v>17</v>
       </c>
-      <c r="E71" s="3">
+      <c r="E71" s="2">
         <v>27.908646000000001</v>
       </c>
-      <c r="F71" s="3">
+      <c r="F71" s="2">
         <v>-82.731842</v>
       </c>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>230</v>
       </c>
@@ -4703,16 +4960,16 @@
       <c r="D72" t="s">
         <v>17</v>
       </c>
-      <c r="E72" s="3">
+      <c r="E72" s="2">
         <v>27.91958</v>
       </c>
-      <c r="F72" s="3">
+      <c r="F72" s="2">
         <v>-82.719750000000005</v>
       </c>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>231</v>
+        <v>290</v>
       </c>
       <c r="B73" t="s">
         <v>128</v>
@@ -4723,16 +4980,16 @@
       <c r="D73" t="s">
         <v>18</v>
       </c>
-      <c r="E73" s="3">
-        <v>27.884336000000001</v>
-      </c>
-      <c r="F73" s="3">
-        <v>-82.667529000000002</v>
-      </c>
-    </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="E73" s="2">
+        <v>27.894607000000001</v>
+      </c>
+      <c r="F73">
+        <v>-82.679820000000007</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B74" t="s">
         <v>128</v>
@@ -4743,16 +5000,16 @@
       <c r="D74" t="s">
         <v>18</v>
       </c>
-      <c r="E74" s="3">
-        <v>27.872796999999998</v>
-      </c>
-      <c r="F74" s="3">
-        <v>-82.651881000000003</v>
-      </c>
-    </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="E74" s="2">
+        <v>27.884336000000001</v>
+      </c>
+      <c r="F74" s="2">
+        <v>-82.667529000000002</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B75" t="s">
         <v>128</v>
@@ -4763,56 +5020,56 @@
       <c r="D75" t="s">
         <v>18</v>
       </c>
-      <c r="E75" s="3">
+      <c r="E75" s="2">
+        <v>27.872796999999998</v>
+      </c>
+      <c r="F75" s="2">
+        <v>-82.651881000000003</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>233</v>
+      </c>
+      <c r="B76" t="s">
+        <v>128</v>
+      </c>
+      <c r="C76" t="s">
+        <v>32</v>
+      </c>
+      <c r="D76" t="s">
+        <v>18</v>
+      </c>
+      <c r="E76" s="2">
         <v>27.907501</v>
       </c>
-      <c r="F75" s="3">
+      <c r="F76" s="2">
         <v>-82.676052999999996</v>
       </c>
     </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A76" t="s">
+    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
         <v>234</v>
       </c>
-      <c r="B76" t="s">
+      <c r="B77" t="s">
         <v>91</v>
-      </c>
-      <c r="C76" t="s">
-        <v>35</v>
-      </c>
-      <c r="D76" t="s">
-        <v>19</v>
-      </c>
-      <c r="E76" s="3">
-        <v>27.839032</v>
-      </c>
-      <c r="F76" s="3">
-        <v>-82.752199000000005</v>
-      </c>
-    </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A77" t="s">
-        <v>235</v>
-      </c>
-      <c r="B77" t="s">
-        <v>88</v>
       </c>
       <c r="C77" t="s">
         <v>35</v>
       </c>
       <c r="D77" t="s">
-        <v>20</v>
-      </c>
-      <c r="E77" s="3">
-        <v>27.911902000000001</v>
-      </c>
-      <c r="F77" s="3">
-        <v>-82.700351999999995</v>
-      </c>
-    </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+      <c r="E77" s="2">
+        <v>27.839032</v>
+      </c>
+      <c r="F77" s="2">
+        <v>-82.752199000000005</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B78" t="s">
         <v>88</v>
@@ -4823,56 +5080,56 @@
       <c r="D78" t="s">
         <v>20</v>
       </c>
-      <c r="E78" s="3">
-        <v>27.882256999999999</v>
-      </c>
-      <c r="F78" s="3">
-        <v>-82.715112000000005</v>
-      </c>
-    </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="E78" s="2">
+        <v>27.911902000000001</v>
+      </c>
+      <c r="F78" s="2">
+        <v>-82.700351999999995</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B79" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="C79" t="s">
         <v>35</v>
       </c>
       <c r="D79" t="s">
+        <v>20</v>
+      </c>
+      <c r="E79" s="2">
+        <v>27.882256999999999</v>
+      </c>
+      <c r="F79" s="2">
+        <v>-82.715112000000005</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>237</v>
+      </c>
+      <c r="B80" t="s">
+        <v>91</v>
+      </c>
+      <c r="C80" t="s">
+        <v>35</v>
+      </c>
+      <c r="D80" t="s">
         <v>19</v>
       </c>
-      <c r="E79" s="3">
+      <c r="E80" s="2">
         <v>27.871178</v>
       </c>
-      <c r="F79" s="3">
+      <c r="F80" s="2">
         <v>-82.729363000000006</v>
       </c>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A80" t="s">
+    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
         <v>238</v>
-      </c>
-      <c r="B80" t="s">
-        <v>127</v>
-      </c>
-      <c r="C80" t="s">
-        <v>32</v>
-      </c>
-      <c r="D80" t="s">
-        <v>21</v>
-      </c>
-      <c r="E80" s="3">
-        <v>27.894496</v>
-      </c>
-      <c r="F80" s="3">
-        <v>-82.776813000000004</v>
-      </c>
-    </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A81" t="s">
-        <v>239</v>
       </c>
       <c r="B81" t="s">
         <v>127</v>
@@ -4883,16 +5140,16 @@
       <c r="D81" t="s">
         <v>21</v>
       </c>
-      <c r="E81" s="3">
-        <v>27.839531999999998</v>
-      </c>
-      <c r="F81" s="3">
-        <v>-82.771511000000004</v>
-      </c>
-    </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="E81" s="2">
+        <v>27.894496</v>
+      </c>
+      <c r="F81" s="2">
+        <v>-82.776813000000004</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B82" t="s">
         <v>127</v>
@@ -4903,16 +5160,16 @@
       <c r="D82" t="s">
         <v>21</v>
       </c>
-      <c r="E82" s="3">
-        <v>27.850125999999999</v>
-      </c>
-      <c r="F82" s="3">
-        <v>-82.772942999999998</v>
-      </c>
-    </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="E82" s="2">
+        <v>27.839531999999998</v>
+      </c>
+      <c r="F82" s="2">
+        <v>-82.771511000000004</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B83" t="s">
         <v>127</v>
@@ -4923,276 +5180,276 @@
       <c r="D83" t="s">
         <v>21</v>
       </c>
-      <c r="E83" s="3">
+      <c r="E83" s="2">
+        <v>27.850125999999999</v>
+      </c>
+      <c r="F83" s="2">
+        <v>-82.772942999999998</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>241</v>
+      </c>
+      <c r="B84" t="s">
+        <v>127</v>
+      </c>
+      <c r="C84" t="s">
+        <v>32</v>
+      </c>
+      <c r="D84" t="s">
+        <v>21</v>
+      </c>
+      <c r="E84" s="2">
         <v>27.90156</v>
       </c>
-      <c r="F83" s="3">
+      <c r="F84" s="2">
         <v>-82.772739999999999</v>
       </c>
     </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A84" t="s">
+    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
         <v>242</v>
       </c>
-      <c r="B84" t="s">
+      <c r="B85" t="s">
         <v>90</v>
       </c>
-      <c r="C84" t="s">
+      <c r="C85" t="s">
         <v>35</v>
       </c>
-      <c r="D84" t="s">
+      <c r="D85" t="s">
         <v>243</v>
       </c>
-      <c r="E84" s="3">
+      <c r="E85" s="2">
         <v>27.903523</v>
       </c>
-      <c r="F84" s="3">
+      <c r="F85" s="2">
         <v>-82.822490999999999</v>
       </c>
     </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A85" t="s">
+    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
         <v>244</v>
       </c>
-      <c r="B85" t="s">
+      <c r="B86" t="s">
         <v>245</v>
       </c>
-      <c r="C85" t="s">
-        <v>32</v>
-      </c>
-      <c r="D85" t="s">
+      <c r="C86" t="s">
+        <v>32</v>
+      </c>
+      <c r="D86" t="s">
         <v>246</v>
       </c>
-      <c r="E85" s="3">
+      <c r="E86" s="2">
         <v>27.892914999999999</v>
       </c>
-      <c r="F85" s="3">
+      <c r="F86" s="2">
         <v>-82.807484000000002</v>
       </c>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A86" t="s">
+    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
         <v>247</v>
       </c>
-      <c r="B86" t="s">
+      <c r="B87" t="s">
         <v>92</v>
       </c>
-      <c r="C86" t="s">
-        <v>32</v>
-      </c>
-      <c r="D86" t="s">
+      <c r="C87" t="s">
+        <v>32</v>
+      </c>
+      <c r="D87" t="s">
         <v>22</v>
       </c>
-      <c r="E86" s="3">
+      <c r="E87" s="2">
         <v>27.891048000000001</v>
       </c>
-      <c r="F86" s="3">
+      <c r="F87" s="2">
         <v>-82.824898000000005</v>
       </c>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A87" t="s">
+    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
         <v>248</v>
       </c>
-      <c r="B87" t="s">
+      <c r="B88" t="s">
         <v>131</v>
       </c>
-      <c r="C87" t="s">
-        <v>32</v>
-      </c>
-      <c r="D87" t="s">
+      <c r="C88" t="s">
+        <v>32</v>
+      </c>
+      <c r="D88" t="s">
         <v>30</v>
       </c>
-      <c r="E87" s="3">
+      <c r="E88" s="2">
         <v>27.915959999999998</v>
       </c>
-      <c r="F87" s="3">
+      <c r="F88" s="2">
         <v>-82.808897000000002</v>
       </c>
     </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A88" t="s">
+    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
         <v>249</v>
       </c>
-      <c r="B88" t="s">
+      <c r="B89" t="s">
         <v>130</v>
       </c>
-      <c r="C88" t="s">
-        <v>32</v>
-      </c>
-      <c r="D88" t="s">
+      <c r="C89" t="s">
+        <v>32</v>
+      </c>
+      <c r="D89" t="s">
         <v>142</v>
       </c>
-      <c r="E88" s="3">
+      <c r="E89" s="2">
         <v>27.8797999999999</v>
       </c>
-      <c r="F88" s="3">
+      <c r="F89" s="2">
         <v>-82.809510000000003</v>
       </c>
     </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A89" t="s">
+    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
         <v>250</v>
       </c>
-      <c r="B89" t="s">
+      <c r="B90" t="s">
         <v>131</v>
       </c>
-      <c r="C89" t="s">
-        <v>32</v>
-      </c>
-      <c r="D89" t="s">
+      <c r="C90" t="s">
+        <v>32</v>
+      </c>
+      <c r="D90" t="s">
         <v>30</v>
       </c>
-      <c r="E89" s="3">
+      <c r="E90" s="2">
         <v>27.912120000000002</v>
       </c>
-      <c r="F89" s="3">
+      <c r="F90" s="2">
         <v>-82.813869999999994</v>
       </c>
     </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A90" t="s">
+    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
         <v>251</v>
       </c>
-      <c r="B90" t="s">
+      <c r="B91" t="s">
         <v>130</v>
       </c>
-      <c r="C90" t="s">
-        <v>32</v>
-      </c>
-      <c r="D90" t="s">
+      <c r="C91" t="s">
+        <v>32</v>
+      </c>
+      <c r="D91" t="s">
         <v>142</v>
       </c>
-      <c r="E90" s="3">
+      <c r="E91" s="2">
         <v>27.894953000000001</v>
       </c>
-      <c r="F90" s="3">
+      <c r="F91" s="2">
         <v>-82.808066999999696</v>
       </c>
     </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A91" t="s">
+    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
         <v>252</v>
       </c>
-      <c r="B91" t="s">
+      <c r="B92" t="s">
         <v>90</v>
       </c>
-      <c r="C91" t="s">
+      <c r="C92" t="s">
         <v>35</v>
       </c>
-      <c r="D91" t="s">
+      <c r="D92" t="s">
         <v>243</v>
       </c>
-      <c r="E91" s="3">
+      <c r="E92" s="2">
         <v>27.90765</v>
       </c>
-      <c r="F91" s="3">
+      <c r="F92" s="2">
         <v>-82.816580000000002</v>
       </c>
     </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A92" t="s">
+    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
         <v>253</v>
       </c>
-      <c r="B92" t="s">
+      <c r="B93" t="s">
         <v>130</v>
       </c>
-      <c r="C92" t="s">
-        <v>32</v>
-      </c>
-      <c r="D92" t="s">
+      <c r="C93" t="s">
+        <v>32</v>
+      </c>
+      <c r="D93" t="s">
         <v>30</v>
       </c>
-      <c r="E92" s="3">
+      <c r="E93" s="2">
         <v>27.913245</v>
       </c>
-      <c r="F92" s="3">
+      <c r="F93" s="2">
         <v>-82.804545000000005</v>
       </c>
     </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A93" t="s">
+    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
         <v>254</v>
       </c>
-      <c r="B93" t="s">
+      <c r="B94" t="s">
         <v>255</v>
       </c>
-      <c r="C93" t="s">
-        <v>32</v>
-      </c>
-      <c r="D93" t="s">
+      <c r="C94" t="s">
+        <v>32</v>
+      </c>
+      <c r="D94" t="s">
         <v>23</v>
       </c>
-      <c r="E93" s="3">
+      <c r="E94" s="2">
         <v>27.849830000000001</v>
       </c>
-      <c r="F93" s="3">
+      <c r="F94" s="2">
         <v>-82.72242</v>
       </c>
     </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A94" t="s">
+    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
         <v>256</v>
       </c>
-      <c r="B94" t="s">
+      <c r="B95" t="s">
         <v>94</v>
       </c>
-      <c r="C94" t="s">
+      <c r="C95" t="s">
         <v>35</v>
       </c>
-      <c r="D94" t="s">
+      <c r="D95" t="s">
         <v>257</v>
       </c>
-      <c r="E94" s="3">
+      <c r="E95" s="2">
         <v>27.808412000000001</v>
       </c>
-      <c r="F94" s="3">
+      <c r="F95" s="2">
         <v>-82.616264999999999</v>
       </c>
     </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A95" t="s">
+    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
         <v>258</v>
       </c>
-      <c r="B95" t="s">
+      <c r="B96" t="s">
         <v>259</v>
       </c>
-      <c r="C95" t="s">
-        <v>32</v>
-      </c>
-      <c r="D95" t="s">
+      <c r="C96" t="s">
+        <v>32</v>
+      </c>
+      <c r="D96" t="s">
         <v>24</v>
       </c>
-      <c r="E95" s="3">
+      <c r="E96" s="2">
         <v>27.840630000000001</v>
       </c>
-      <c r="F95" s="3">
+      <c r="F96" s="2">
         <v>-82.728945999999993</v>
       </c>
     </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A96" t="s">
+    <row r="97" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
         <v>260</v>
-      </c>
-      <c r="B96" t="s">
-        <v>135</v>
-      </c>
-      <c r="C96" t="s">
-        <v>32</v>
-      </c>
-      <c r="D96" t="s">
-        <v>25</v>
-      </c>
-      <c r="E96" s="3">
-        <v>27.821999999999999</v>
-      </c>
-      <c r="F96" s="3">
-        <v>-82.736000000000004</v>
-      </c>
-    </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A97" t="s">
-        <v>261</v>
       </c>
       <c r="B97" t="s">
         <v>135</v>
@@ -5203,36 +5460,36 @@
       <c r="D97" t="s">
         <v>25</v>
       </c>
-      <c r="E97" s="3">
+      <c r="E97" s="2">
+        <v>27.821999999999999</v>
+      </c>
+      <c r="F97" s="2">
+        <v>-82.736000000000004</v>
+      </c>
+    </row>
+    <row r="98" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>261</v>
+      </c>
+      <c r="B98" t="s">
+        <v>135</v>
+      </c>
+      <c r="C98" t="s">
+        <v>32</v>
+      </c>
+      <c r="D98" t="s">
+        <v>25</v>
+      </c>
+      <c r="E98" s="2">
         <v>27.824248000000001</v>
       </c>
-      <c r="F97" s="3">
+      <c r="F98" s="2">
         <v>-82.731661000000003</v>
       </c>
     </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A98" t="s">
+    <row r="99" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
         <v>262</v>
-      </c>
-      <c r="B98" t="s">
-        <v>133</v>
-      </c>
-      <c r="C98" t="s">
-        <v>32</v>
-      </c>
-      <c r="D98" t="s">
-        <v>26</v>
-      </c>
-      <c r="E98" s="3">
-        <v>27.809920000000002</v>
-      </c>
-      <c r="F98" s="3">
-        <v>-82.720528000000002</v>
-      </c>
-    </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A99" t="s">
-        <v>263</v>
       </c>
       <c r="B99" t="s">
         <v>133</v>
@@ -5243,16 +5500,16 @@
       <c r="D99" t="s">
         <v>26</v>
       </c>
-      <c r="E99" s="3">
-        <v>27.813779</v>
-      </c>
-      <c r="F99" s="3">
-        <v>-82.695728000000003</v>
-      </c>
-    </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="E99" s="2">
+        <v>27.809920000000002</v>
+      </c>
+      <c r="F99" s="2">
+        <v>-82.720528000000002</v>
+      </c>
+    </row>
+    <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B100" t="s">
         <v>133</v>
@@ -5263,16 +5520,16 @@
       <c r="D100" t="s">
         <v>26</v>
       </c>
-      <c r="E100" s="3">
-        <v>27.803728</v>
-      </c>
-      <c r="F100" s="3">
-        <v>-82.724119999999999</v>
-      </c>
-    </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="E100" s="2">
+        <v>27.813779</v>
+      </c>
+      <c r="F100" s="2">
+        <v>-82.695728000000003</v>
+      </c>
+    </row>
+    <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B101" t="s">
         <v>133</v>
@@ -5283,16 +5540,16 @@
       <c r="D101" t="s">
         <v>26</v>
       </c>
-      <c r="E101" s="3">
-        <v>27.809809999999999</v>
-      </c>
-      <c r="F101" s="3">
-        <v>-82.732685000000004</v>
-      </c>
-    </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="E101" s="2">
+        <v>27.803728</v>
+      </c>
+      <c r="F101" s="2">
+        <v>-82.724119999999999</v>
+      </c>
+    </row>
+    <row r="102" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B102" t="s">
         <v>133</v>
@@ -5303,216 +5560,216 @@
       <c r="D102" t="s">
         <v>26</v>
       </c>
-      <c r="E102" s="3">
+      <c r="E102" s="2">
+        <v>27.809809999999999</v>
+      </c>
+      <c r="F102" s="2">
+        <v>-82.732685000000004</v>
+      </c>
+    </row>
+    <row r="103" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>266</v>
+      </c>
+      <c r="B103" t="s">
+        <v>133</v>
+      </c>
+      <c r="C103" t="s">
+        <v>32</v>
+      </c>
+      <c r="D103" t="s">
+        <v>26</v>
+      </c>
+      <c r="E103" s="2">
         <v>27.816203000000002</v>
       </c>
-      <c r="F102" s="3">
+      <c r="F103" s="2">
         <v>-82.683394000000007</v>
       </c>
     </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A103" t="s">
+    <row r="104" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
         <v>267</v>
       </c>
-      <c r="B103" t="s">
+      <c r="B104" t="s">
         <v>268</v>
       </c>
-      <c r="C103" t="s">
+      <c r="C104" t="s">
         <v>35</v>
       </c>
-      <c r="D103" t="s">
+      <c r="D104" t="s">
         <v>269</v>
       </c>
-      <c r="E103" s="3">
+      <c r="E104" s="2">
         <v>27.757975999999999</v>
       </c>
-      <c r="F103" s="3">
+      <c r="F104" s="2">
         <v>-82.731505999999996</v>
       </c>
     </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A104" t="s">
+    <row r="105" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
         <v>270</v>
       </c>
-      <c r="B104" t="s">
+      <c r="B105" t="s">
         <v>271</v>
       </c>
-      <c r="C104" t="s">
-        <v>32</v>
-      </c>
-      <c r="D104" t="s">
+      <c r="C105" t="s">
+        <v>32</v>
+      </c>
+      <c r="D105" t="s">
         <v>272</v>
       </c>
-      <c r="E104" s="3">
+      <c r="E105" s="2">
         <v>27.764379999999999</v>
       </c>
-      <c r="F104" s="3">
+      <c r="F105" s="2">
         <v>-82.720281</v>
       </c>
     </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A105" t="s">
+    <row r="106" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
         <v>273</v>
       </c>
-      <c r="B105" t="s">
+      <c r="B106" t="s">
         <v>268</v>
       </c>
-      <c r="C105" t="s">
+      <c r="C106" t="s">
         <v>35</v>
       </c>
-      <c r="D105" t="s">
+      <c r="D106" t="s">
         <v>269</v>
       </c>
-      <c r="E105" s="3">
+      <c r="E106" s="2">
         <v>27.760207000000001</v>
       </c>
-      <c r="F105" s="3">
+      <c r="F106" s="2">
         <v>-82.729787000000002</v>
       </c>
     </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A106" t="s">
+    <row r="107" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
         <v>274</v>
       </c>
-      <c r="B106" t="s">
+      <c r="B107" t="s">
         <v>95</v>
       </c>
-      <c r="C106" t="s">
-        <v>32</v>
-      </c>
-      <c r="D106" t="s">
+      <c r="C107" t="s">
+        <v>32</v>
+      </c>
+      <c r="D107" t="s">
         <v>275</v>
       </c>
-      <c r="E106" s="3">
+      <c r="E107" s="2">
         <v>27.760513</v>
       </c>
-      <c r="F106" s="3">
+      <c r="F107" s="2">
         <v>-82.642373000000006</v>
       </c>
     </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A107" t="s">
+    <row r="108" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
         <v>276</v>
       </c>
-      <c r="B107" t="s">
+      <c r="B108" t="s">
         <v>96</v>
       </c>
-      <c r="C107" t="s">
+      <c r="C108" t="s">
         <v>35</v>
       </c>
-      <c r="D107" t="s">
+      <c r="D108" t="s">
         <v>277</v>
       </c>
-      <c r="E107" s="3">
+      <c r="E108" s="2">
         <v>27.792266000000001</v>
       </c>
-      <c r="F107" s="3">
+      <c r="F108" s="2">
         <v>-82.626583999999994</v>
       </c>
     </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A108" t="s">
+    <row r="109" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
         <v>278</v>
       </c>
-      <c r="B108" t="s">
+      <c r="B109" t="s">
         <v>140</v>
       </c>
-      <c r="C108" t="s">
-        <v>32</v>
-      </c>
-      <c r="D108" t="s">
+      <c r="C109" t="s">
+        <v>32</v>
+      </c>
+      <c r="D109" t="s">
         <v>31</v>
       </c>
-      <c r="E108" s="3">
+      <c r="E109" s="2">
         <v>27.7593</v>
       </c>
-      <c r="F108" s="3">
+      <c r="F109" s="2">
         <v>-82.681276999999994</v>
       </c>
     </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A109" t="s">
+    <row r="110" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
         <v>281</v>
       </c>
-      <c r="B109" t="s">
+      <c r="B110" t="s">
         <v>280</v>
-      </c>
-      <c r="C109" t="s">
-        <v>35</v>
-      </c>
-      <c r="D109" t="s">
-        <v>279</v>
-      </c>
-      <c r="E109" s="3">
-        <v>27.748215999999999</v>
-      </c>
-      <c r="F109" s="3">
-        <v>-82.688475999999994</v>
-      </c>
-    </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A110" t="s">
-        <v>282</v>
-      </c>
-      <c r="B110" t="s">
-        <v>283</v>
       </c>
       <c r="C110" t="s">
         <v>35</v>
       </c>
       <c r="D110" t="s">
-        <v>34</v>
-      </c>
-      <c r="E110" s="3">
-        <v>27.711438000000001</v>
-      </c>
-      <c r="F110" s="3">
-        <v>-82.684027</v>
-      </c>
-    </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.3">
+        <v>279</v>
+      </c>
+      <c r="E110" s="2">
+        <v>27.748215999999999</v>
+      </c>
+      <c r="F110" s="2">
+        <v>-82.688475999999994</v>
+      </c>
+    </row>
+    <row r="111" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="B111" t="s">
-        <v>138</v>
+        <v>283</v>
       </c>
       <c r="C111" t="s">
         <v>35</v>
       </c>
       <c r="D111" t="s">
-        <v>33</v>
-      </c>
-      <c r="E111" s="3">
-        <v>27.717371</v>
-      </c>
-      <c r="F111" s="3">
-        <v>-82.642402000000004</v>
-      </c>
-    </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.3">
+        <v>34</v>
+      </c>
+      <c r="E111" s="2">
+        <v>27.711438000000001</v>
+      </c>
+      <c r="F111" s="2">
+        <v>-82.684027</v>
+      </c>
+    </row>
+    <row r="112" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B112" t="s">
-        <v>286</v>
+        <v>138</v>
       </c>
       <c r="C112" t="s">
         <v>35</v>
       </c>
       <c r="D112" t="s">
-        <v>287</v>
-      </c>
-      <c r="E112" s="3">
-        <v>28.106107999999999</v>
-      </c>
-      <c r="F112" s="3">
-        <v>-82.772577999999996</v>
-      </c>
-    </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.3">
+        <v>33</v>
+      </c>
+      <c r="E112" s="2">
+        <v>27.717371</v>
+      </c>
+      <c r="F112" s="2">
+        <v>-82.642402000000004</v>
+      </c>
+    </row>
+    <row r="113" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="B113" t="s">
         <v>286</v>
@@ -5523,10 +5780,30 @@
       <c r="D113" t="s">
         <v>287</v>
       </c>
-      <c r="E113" s="3">
+      <c r="E113" s="2">
+        <v>28.106107999999999</v>
+      </c>
+      <c r="F113" s="2">
+        <v>-82.772577999999996</v>
+      </c>
+    </row>
+    <row r="114" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A114" t="s">
+        <v>288</v>
+      </c>
+      <c r="B114" t="s">
+        <v>286</v>
+      </c>
+      <c r="C114" t="s">
+        <v>35</v>
+      </c>
+      <c r="D114" t="s">
+        <v>287</v>
+      </c>
+      <c r="E114" s="2">
         <v>28.106427</v>
       </c>
-      <c r="F113" s="3">
+      <c r="F114" s="2">
         <v>-82.773554000000004</v>
       </c>
     </row>
@@ -5536,19 +5813,17 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="ebcefb84-3943-4c67-86e4-95e0d5522177" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="20a86c8e-58bd-487e-986c-19c6170a5cfd">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100B730D8DC4DFB374C886B31D158660B04" ma:contentTypeVersion="14" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="6c7b2a44c3204d196172482da32476cf">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="20a86c8e-58bd-487e-986c-19c6170a5cfd" xmlns:ns3="ebcefb84-3943-4c67-86e4-95e0d5522177" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="447da8927e53f285c23cc8bbcad2da18" ns2:_="" ns3:_="">
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100B730D8DC4DFB374C886B31D158660B04" ma:contentTypeVersion="14" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="e156938d0b65e910bf65aa8aa145b3eb">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="20a86c8e-58bd-487e-986c-19c6170a5cfd" xmlns:ns3="ebcefb84-3943-4c67-86e4-95e0d5522177" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="258c2e9f717cb07b6517e945f6b981b4" ns2:_="" ns3:_="">
     <xsd:import namespace="20a86c8e-58bd-487e-986c-19c6170a5cfd"/>
     <xsd:import namespace="ebcefb84-3943-4c67-86e4-95e0d5522177"/>
     <xsd:element name="properties">
@@ -5760,15 +6035,44 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="ebcefb84-3943-4c67-86e4-95e0d5522177" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="20a86c8e-58bd-487e-986c-19c6170a5cfd">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{45BDAAEB-4F8C-4301-B90B-EF9ABD213FC8}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9BC217A0-75D3-4565-BA0D-77A510477165}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="20a86c8e-58bd-487e-986c-19c6170a5cfd"/>
+    <ds:schemaRef ds:uri="ebcefb84-3943-4c67-86e4-95e0d5522177"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{67C3CBFC-B408-4AC6-998F-0F89C93E332F}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
@@ -5777,16 +6081,4 @@
     <ds:schemaRef ds:uri="20a86c8e-58bd-487e-986c-19c6170a5cfd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8AC533CB-CDFA-44DE-A983-8E3AE0E5EB45}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{45BDAAEB-4F8C-4301-B90B-EF9ABD213FC8}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>